--- a/vehicle_data.xlsx
+++ b/vehicle_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,6 +465,91 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>RTB RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>18-07-2026 09:29:04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ram</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>23027</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Safari</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>18-07-2026 09:29:38</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ram</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>63553</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Safari</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Moulting RH Front, Damper RH, Subframe RH Rear</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>18-07-2026 11:00:41</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ram</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>29577</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Harrier</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Damper LH</t>
         </is>
       </c>
     </row>
